--- a/data/fmsForecastOutput/File1/RPT_RPT5649048177252MG_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT5649048177252MG_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>434.5012921620497</v>
+        <v>432.4379596572089</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>467.2185453012282</v>
+        <v>464.7927072399157</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>503.5452877216155</v>
+        <v>501.1273427237671</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>568.731870694428</v>
+        <v>565.3430834368205</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>614.3758369998579</v>
+        <v>609.0701680022856</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>434.5012921620497</v>
+        <v>432.4379596572089</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>467.2185453012282</v>
+        <v>464.7927072399157</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>503.5452877216155</v>
+        <v>501.1273427237671</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>568.731870694428</v>
+        <v>565.3430834368205</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>614.3758369998579</v>
+        <v>609.0701680022856</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>7024521.211587961</v>
+        <v>6991163.605504232</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>8294787.470846929</v>
+        <v>8251720.235268116</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>9577994.053480431</v>
+        <v>9532002.037715927</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>11048121.26871937</v>
+        <v>10982291.06910312</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>12761392.30232979</v>
+        <v>12651186.59529066</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>540.4425765023692</v>
+        <v>537.8761566660817</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>581.1370391002466</v>
+        <v>578.1197266188276</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>626.3210664524368</v>
+        <v>623.3135715426383</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>707.4016190093972</v>
+        <v>703.18656844509</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>764.1746210622744</v>
+        <v>757.5753094495318</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>540.4425765023692</v>
+        <v>537.8761566660817</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>581.1370391002466</v>
+        <v>578.1197266188276</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>626.3210664524368</v>
+        <v>623.3135715426383</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>707.4016190093972</v>
+        <v>703.18656844509</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>764.1746210622744</v>
+        <v>757.5753094495318</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>7024521.211587961</v>
+        <v>6991163.605504232</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>8294787.470846929</v>
+        <v>8251720.235268116</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>9577994.053480431</v>
+        <v>9532002.037715927</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>11048121.26871937</v>
+        <v>10982291.06910312</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>12761392.30232979</v>
+        <v>12651186.59529066</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>851.2908447100559</v>
+        <v>850.1973778349502</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>935.3378843660278</v>
+        <v>934.0355079180465</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1013.436084975897</v>
+        <v>1012.131908980887</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1278.882916645338</v>
+        <v>1276.80334985947</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1376.329762012949</v>
+        <v>1373.153184967183</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>851.2908447100559</v>
+        <v>850.1973778349502</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>935.3378843660278</v>
+        <v>934.0355079180465</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>1013.436084975897</v>
+        <v>1012.131908980887</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>1278.882916645338</v>
+        <v>1276.80334985947</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>1376.329762012949</v>
+        <v>1373.153184967183</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>2842420.624140603</v>
+        <v>2838769.588989774</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>3335182.545451042</v>
+        <v>3330538.594564932</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>3844631.692550807</v>
+        <v>3839684.092561611</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>4298566.961883924</v>
+        <v>4291577.145252227</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>4972032.844337074</v>
+        <v>4960557.363794521</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>1034.571334378072</v>
+        <v>1033.242447205015</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1136.713461839834</v>
+        <v>1135.130687458994</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1231.625982184156</v>
+        <v>1230.041020818948</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1554.222759247135</v>
+        <v>1551.695467666411</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1672.649632353283</v>
+        <v>1668.789147334074</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>1034.571334378072</v>
+        <v>1033.242447205015</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>1136.713461839834</v>
+        <v>1135.130687458994</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>1231.625982184156</v>
+        <v>1230.041020818948</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>1554.222759247135</v>
+        <v>1551.695467666411</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1672.649632353283</v>
+        <v>1668.789147334074</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>2842420.624140603</v>
+        <v>2838769.588989774</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>3335182.545451042</v>
+        <v>3330538.594564932</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>3844631.692550807</v>
+        <v>3839684.092561611</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>4298566.961883924</v>
+        <v>4291577.145252227</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>4972032.844337074</v>
+        <v>4960557.363794521</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>505.8462286043429</v>
+        <v>503.9489151402576</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>545.5136679300806</v>
+        <v>543.2757340150918</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>588.330345305111</v>
+        <v>586.0975987253336</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>673.4821131359637</v>
+        <v>670.2864413607681</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>727.2613096618846</v>
+        <v>722.2710712217657</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>505.8462286043429</v>
+        <v>503.9489151402576</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>545.5136679300806</v>
+        <v>543.2757340150918</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>588.330345305111</v>
+        <v>586.0975987253336</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>673.4821131359637</v>
+        <v>670.2864413607681</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>727.2613096618846</v>
+        <v>722.2710712217657</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>9866941.835728563</v>
+        <v>9829933.194494003</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>11629970.01629797</v>
+        <v>11582258.82983305</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>13422625.74603124</v>
+        <v>13371686.13027754</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>15346688.2306033</v>
+        <v>15273868.21435535</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>17733425.14666686</v>
+        <v>17611743.95908518</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>626.6651567050234</v>
+        <v>624.3146790854313</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>675.8689538634852</v>
+        <v>673.0962459684138</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>728.9336489161107</v>
+        <v>726.1673049318341</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>834.80207170569</v>
+        <v>830.840936931074</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>901.449388937761</v>
+        <v>895.2639266661733</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>626.6651567050234</v>
+        <v>624.3146790854313</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>675.8689538634852</v>
+        <v>673.0962459684138</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>728.9336489161107</v>
+        <v>726.1673049318341</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>834.80207170569</v>
+        <v>830.840936931074</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>901.449388937761</v>
+        <v>895.2639266661733</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>9866941.835728563</v>
+        <v>9829933.194494003</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>11629970.01629797</v>
+        <v>11582258.82983305</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>13422625.74603124</v>
+        <v>13371686.13027754</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>15346688.2306033</v>
+        <v>15273868.21435535</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>17733425.14666686</v>
+        <v>17611743.95908518</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>1147.139649219559</v>
+        <v>1146.584218233141</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>1258.698041141888</v>
+        <v>1258.037606928285</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1352.656063222845</v>
+        <v>1352.017935630586</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1466.908042089006</v>
+        <v>1466.06445973549</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>1558.210524526686</v>
+        <v>1556.954463953512</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>1147.139649219559</v>
+        <v>1146.584218233141</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>1258.698041141888</v>
+        <v>1258.037606928285</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>1352.656063222845</v>
+        <v>1352.017935630586</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>1466.908042089006</v>
+        <v>1466.06445973549</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>1558.210524526686</v>
+        <v>1556.954463953512</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>108159.2265587395</v>
+        <v>108106.8571842359</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>129684.8460897693</v>
+        <v>129616.800929974</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>154313.0542159432</v>
+        <v>154240.2556528655</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>183269.1963916292</v>
+        <v>183163.8028321264</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>221699.0632124929</v>
+        <v>221520.3534373837</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1174.044843550935</v>
+        <v>1173.476385398523</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1288.219743599373</v>
+        <v>1287.543819457519</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1384.381471955151</v>
+        <v>1383.728377617657</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1501.313134760603</v>
+        <v>1500.449766893465</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1594.757040027312</v>
+        <v>1593.47151961127</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>1174.044843550935</v>
+        <v>1173.476385398523</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1288.219743599373</v>
+        <v>1287.543819457519</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>1384.381471955151</v>
+        <v>1383.728377617657</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>1501.313134760603</v>
+        <v>1500.449766893465</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>1594.757040027312</v>
+        <v>1593.47151961127</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>108159.2265587395</v>
+        <v>108106.8571842359</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>129684.8460897693</v>
+        <v>129616.800929974</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>154313.0542159432</v>
+        <v>154240.2556528655</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>183269.1963916292</v>
+        <v>183163.8028321264</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>221699.0632124929</v>
+        <v>221520.3534373837</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>508.9311620983621</v>
+        <v>507.0403037421377</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>548.9437360999096</v>
+        <v>546.713389187268</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>592.1332138932725</v>
+        <v>589.9084012692884</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>677.8085438061919</v>
+        <v>674.6256976161476</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>732.0817126945633</v>
+        <v>727.1131365197093</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>508.9311620983621</v>
+        <v>507.0403037421377</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>548.9437360999096</v>
+        <v>546.713389187268</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>592.1332138932725</v>
+        <v>589.9084012692884</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>677.8085438061919</v>
+        <v>674.6256976161476</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>732.0817126945633</v>
+        <v>727.1131365197093</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>9975101.062287301</v>
+        <v>9938040.05167824</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>11759654.86238774</v>
+        <v>11711875.63076302</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>13576938.80024718</v>
+        <v>13525926.3859304</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>15529957.42699493</v>
+        <v>15457032.01718747</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>17955124.20987936</v>
+        <v>17833264.31252256</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>629.8492580487008</v>
+        <v>627.5091464158569</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>679.4305944000877</v>
+        <v>676.6700821127254</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>732.8774455338701</v>
+        <v>730.1238168665363</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>839.198703465826</v>
+        <v>835.2580030712614</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>906.3144220446239</v>
+        <v>900.1633433245684</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>629.8492580487008</v>
+        <v>627.5091464158569</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>679.4305944000877</v>
+        <v>676.6700821127254</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>732.8774455338701</v>
+        <v>730.1238168665363</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>839.198703465826</v>
+        <v>835.2580030712614</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>906.3144220446239</v>
+        <v>900.1633433245684</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>9975101.062287301</v>
+        <v>9938040.05167824</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>11759654.86238774</v>
+        <v>11711875.63076302</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>13576938.80024718</v>
+        <v>13525926.3859304</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>15529957.42699493</v>
+        <v>15457032.01718747</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>17955124.20987936</v>
+        <v>17833264.31252256</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>508.9245628369225</v>
+        <v>507.0338186788888</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>548.9368513205744</v>
+        <v>546.7066308537917</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>592.125854700685</v>
+        <v>589.9011635029074</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>677.7978047398461</v>
+        <v>674.6151359167377</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>732.070410897913</v>
+        <v>727.1020986258922</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>508.9245628369225</v>
+        <v>507.0338186788888</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>548.9368513205744</v>
+        <v>546.7066308537917</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>592.125854700685</v>
+        <v>589.9011635029074</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>677.7978047398461</v>
+        <v>674.6151359167377</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>732.070410897913</v>
+        <v>727.1020986258922</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>9975574.189860687</v>
+        <v>9938513.179251626</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>11760174.09813562</v>
+        <v>11712394.86651091</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>13577511.09809858</v>
+        <v>13526498.6837818</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>15530576.82859054</v>
+        <v>15457651.41878308</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>17955800.73184001</v>
+        <v>17833940.83448322</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>629.8265076729132</v>
+        <v>627.4865915499438</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>679.4073011605203</v>
+        <v>676.6470053911899</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>732.8529983502012</v>
+        <v>730.099577600623</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>839.1674523169787</v>
+        <v>835.2270558312131</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>906.2819540428497</v>
+        <v>900.1313274266757</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>629.8265076729132</v>
+        <v>627.4865915499438</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>679.4073011605203</v>
+        <v>676.6470053911899</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>732.8529983502012</v>
+        <v>730.099577600623</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>839.1674523169787</v>
+        <v>835.2270558312131</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>906.2819540428497</v>
+        <v>900.1313274266757</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>9975574.189860687</v>
+        <v>9938513.179251626</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>11760174.09813562</v>
+        <v>11712394.86651091</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>13577511.09809858</v>
+        <v>13526498.6837818</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>15530576.82859054</v>
+        <v>15457651.41878308</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>17955800.73184001</v>
+        <v>17833940.83448322</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>442.6589644523504</v>
+        <v>442.6509216134133</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>486.7414921450909</v>
+        <v>486.7333462292817</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>527.9634489735078</v>
+        <v>527.9550045796614</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>605.475825935625</v>
+        <v>605.4667008589784</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>654.1626749879557</v>
+        <v>654.1532519168434</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>442.6589644523504</v>
+        <v>442.6509216134133</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>486.7414921450909</v>
+        <v>486.7333462292817</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>527.9634489735078</v>
+        <v>527.9550045796614</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>605.475825935625</v>
+        <v>605.4667008589784</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>654.1626749879557</v>
+        <v>654.1532519168434</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>7156405.150885956</v>
+        <v>7156275.123441312</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>8641389.06982686</v>
+        <v>8641244.450909069</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>10042454.76629093</v>
+        <v>10042294.14448388</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>11761905.20507847</v>
+        <v>11761727.94236721</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>13587817.13458678</v>
+        <v>13587621.40503507</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>550.589274591331</v>
+        <v>550.5792707255752</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>605.420123831053</v>
+        <v>605.4099917559422</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>656.692930054401</v>
+        <v>656.6824267255279</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>753.1045851447294</v>
+        <v>753.0932351671281</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>813.6623938745828</v>
+        <v>813.6506732446966</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>550.589274591331</v>
+        <v>550.5792707255752</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>605.420123831053</v>
+        <v>605.4099917559422</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>656.692930054401</v>
+        <v>656.6824267255279</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>753.1045851447294</v>
+        <v>753.0932351671281</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>813.6623938745828</v>
+        <v>813.6506732446966</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>7156405.150885956</v>
+        <v>7156275.123441312</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>8641389.06982686</v>
+        <v>8641244.450909069</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>10042454.76629093</v>
+        <v>10042294.14448388</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>11761905.20507847</v>
+        <v>11761727.94236721</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>13587817.13458678</v>
+        <v>13587621.40503507</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>515.0495596789066</v>
+        <v>515.0428935919281</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>567.8047607454694</v>
+        <v>567.7979772717214</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>616.0525054771099</v>
+        <v>616.0454652239587</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>717.9317420013057</v>
+        <v>717.9239629115395</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>775.748184756489</v>
+        <v>775.7401577380795</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>515.0495596789066</v>
+        <v>515.0428935919281</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>567.8047607454694</v>
+        <v>567.7979772717214</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>616.0525054771099</v>
+        <v>616.0454652239587</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>717.9317420013057</v>
+        <v>717.9239629115395</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>775.748184756489</v>
+        <v>775.7401577380795</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>10046460.28871421</v>
+        <v>10046330.26126956</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>12105200.53079117</v>
+        <v>12105055.91187338</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>14055100.65375897</v>
+        <v>14054940.03195192</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>16359565.31056921</v>
+        <v>16359388.04785795</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>18915721.46665906</v>
+        <v>18915525.73710735</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>638.0666589480317</v>
+        <v>638.0584006983803</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>703.4866992423996</v>
+        <v>703.4782947979737</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>763.2810449518061</v>
+        <v>763.2723221696824</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>889.8987721816022</v>
+        <v>889.8891297573623</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>961.5494703594625</v>
+        <v>961.5395207708564</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>638.0666589480317</v>
+        <v>638.0584006983803</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>703.4866992423996</v>
+        <v>703.4782947979737</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>763.2810449518061</v>
+        <v>763.2723221696824</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>889.8987721816022</v>
+        <v>889.8891297573623</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>961.5494703594625</v>
+        <v>961.5395207708564</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>10046460.28871421</v>
+        <v>10046330.26126956</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>12105200.53079117</v>
+        <v>12105055.91187338</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>14055100.65375897</v>
+        <v>14054940.03195192</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>16359565.31056921</v>
+        <v>16359388.04785795</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>18915721.46665906</v>
+        <v>18915525.73710735</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4756,7 +4756,7 @@
         <v>195685.1090677679</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>237255.5176367593</v>
+        <v>237255.5176367592</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>195685.1090677679</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>237255.5176367593</v>
+        <v>237255.5176367592</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>518.2168216654252</v>
+        <v>518.2101876455696</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>571.4099112936353</v>
+        <v>571.4031604450796</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>620.07312362553</v>
+        <v>620.0661184008449</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>722.5576909680124</v>
+        <v>722.5499542964371</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>780.9215926308005</v>
+        <v>780.9136121777683</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>518.2168216654252</v>
+        <v>518.2101876455696</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>571.4099112936353</v>
+        <v>571.4031604450796</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>620.07312362553</v>
+        <v>620.0661184008449</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>722.5576909680124</v>
+        <v>722.5499542964371</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>780.9215926308005</v>
+        <v>780.9136121777683</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>10157100.90727527</v>
+        <v>10156970.87983062</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>12240932.72199714</v>
+        <v>12240788.10307935</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>14217569.04293386</v>
+        <v>14217408.42112681</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>16555250.41963698</v>
+        <v>16555073.15692572</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>19152976.98429582</v>
+        <v>19152781.25474411</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>641.3411182930085</v>
+        <v>641.3329080815005</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>707.2370994423302</v>
+        <v>707.2287438810126</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>767.4583965641133</v>
+        <v>767.4497262665313</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>894.6028830421445</v>
+        <v>894.5933042240337</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>966.7780107254788</v>
+        <v>966.7681309544749</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>641.3411182930085</v>
+        <v>641.3329080815005</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>707.2370994423302</v>
+        <v>707.2287438810126</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>767.4583965641133</v>
+        <v>767.4497262665313</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>894.6028830421445</v>
+        <v>894.5933042240337</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>966.7780107254788</v>
+        <v>966.7681309544749</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>10157100.90727527</v>
+        <v>10156970.87983062</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>12240932.72199714</v>
+        <v>12240788.10307935</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>14217569.04293386</v>
+        <v>14217408.42112681</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>16555250.41963698</v>
+        <v>16555073.15692572</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>19152976.98429582</v>
+        <v>19152781.25474411</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>518.2073206513577</v>
+        <v>518.2006870321632</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>571.4000038462955</v>
+        <v>571.3932533804681</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>620.062669465005</v>
+        <v>620.0556646226523</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>722.5431440593924</v>
+        <v>722.53540781895</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>780.9065114504461</v>
+        <v>780.8985314212907</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>518.2073206513577</v>
+        <v>518.2006870321632</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>571.4000038462955</v>
+        <v>571.3932533804681</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>620.062669465005</v>
+        <v>620.0556646226523</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>722.5431440593924</v>
+        <v>722.53540781895</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>780.9065114504461</v>
+        <v>780.8985314212907</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>10157528.14930061</v>
+        <v>10157398.12185596</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>12241414.4882824</v>
+        <v>12241269.86936461</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>14218105.33916549</v>
+        <v>14217944.71735844</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>16555839.7095913</v>
+        <v>16555662.44688004</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>19153624.4342976</v>
+        <v>19153428.70474588</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>641.314510734209</v>
+        <v>641.3063012086416</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>707.2094605461446</v>
+        <v>707.2011056401872</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>767.4293950771021</v>
+        <v>767.4207254341868</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>894.5657320653978</v>
+        <v>894.5561539860104</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>966.7396313068401</v>
+        <v>966.7297522619988</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>641.314510734209</v>
+        <v>641.3063012086416</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>707.2094605461446</v>
+        <v>707.2011056401872</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>767.4293950771021</v>
+        <v>767.4207254341868</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>894.5657320653978</v>
+        <v>894.5561539860104</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>966.7396313068401</v>
+        <v>966.7297522619988</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>10157528.14930061</v>
+        <v>10157398.12185596</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>12241414.4882824</v>
+        <v>12241269.86936461</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>14218105.33916549</v>
+        <v>14217944.71735844</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>16555839.7095913</v>
+        <v>16555662.44688004</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>19153624.4342976</v>
+        <v>19153428.70474588</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>2.255217639619415</v>
+        <v>0.3030479928119676</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>2.514114528088952</v>
+        <v>0.1928950721971151</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>2.458633606550164</v>
+        <v>0.1410928334452031</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>3.385191997372321</v>
+        <v>0.09962689346713841</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>5.281511648246346</v>
+        <v>0.05691410083355009</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>2.255217639619415</v>
+        <v>0.3030479928119676</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>2.514114528088952</v>
+        <v>0.1928950721971151</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>2.458633606550164</v>
+        <v>0.1410928334452031</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.385191997372321</v>
+        <v>0.09962689346713841</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>5.281511648246346</v>
+        <v>0.05691410083355009</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>36459.7860398206</v>
+        <v>4899.334229926493</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>44634.45618243026</v>
+        <v>3424.572171075029</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>46765.95856904044</v>
+        <v>2683.74335472676</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>65760.35849582673</v>
+        <v>1935.340812370469</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>109703.9271949942</v>
+        <v>1182.180555501657</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>2.805090925425704</v>
+        <v>0.3769379769257131</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>3.127112755917154</v>
+        <v>0.2399272722391336</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>3.058104325507319</v>
+        <v>0.175494471037629</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>4.210578697963403</v>
+        <v>0.1239181930308885</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>6.569264152938316</v>
+        <v>0.07079105137005619</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>2.805090925425704</v>
+        <v>0.3769379769257131</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>3.127112755917154</v>
+        <v>0.2399272722391336</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>3.058104325507319</v>
+        <v>0.175494471037629</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>4.210578697963403</v>
+        <v>0.1239181930308885</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>6.569264152938316</v>
+        <v>0.07079105137005619</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>36459.7860398206</v>
+        <v>4899.334229926493</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>44634.45618243026</v>
+        <v>3424.572171075029</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>46765.95856904044</v>
+        <v>2683.74335472676</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>65760.35849582673</v>
+        <v>1935.340812370469</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>109703.9271949942</v>
+        <v>1182.180555501657</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6436,49 +6436,49 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>1.259339912335955</v>
+        <v>0.2986708527144198</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>1.315268750253711</v>
+        <v>0.1388708570600917</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>1.288372490439024</v>
+        <v>0.1024283644363288</v>
       </c>
       <c r="F58" s="156" t="n">
-        <v>2.015404495667148</v>
+        <v>0.08303917704034666</v>
       </c>
       <c r="G58" s="157" t="n">
-        <v>3.112149410622911</v>
+        <v>0.04725562859493485</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>1.259339912335955</v>
+        <v>0.2986708527144198</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>1.315268750253711</v>
+        <v>0.1388708570600917</v>
       </c>
       <c r="J58" s="156" t="n">
-        <v>1.288372490439024</v>
+        <v>0.1024283644363288</v>
       </c>
       <c r="K58" s="156" t="n">
-        <v>2.015404495667148</v>
+        <v>0.08303917704034666</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>3.112149410622911</v>
+        <v>0.04725562859493485</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>4204.877524374548</v>
+        <v>997.2481166225549</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>4689.921633396324</v>
+        <v>495.1789789339862</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>4887.646869876646</v>
+        <v>388.5783642067765</v>
       </c>
       <c r="P58" s="159" t="n">
-        <v>6774.155059191921</v>
+        <v>279.1103535138191</v>
       </c>
       <c r="Q58" s="160" t="n">
-        <v>11242.73376423273</v>
+        <v>170.7123858966582</v>
       </c>
       <c r="S58" s="32" t="inlineStr">
         <is>
@@ -6486,49 +6486,49 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>1.530472201876815</v>
+        <v>0.3629738350326508</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>1.598442359002721</v>
+        <v>0.1687693563106734</v>
       </c>
       <c r="V58" s="156" t="n">
-        <v>1.565755411199661</v>
+        <v>0.1244808990153637</v>
       </c>
       <c r="W58" s="156" t="n">
-        <v>2.449315332533725</v>
+        <v>0.1009172749009755</v>
       </c>
       <c r="X58" s="157" t="n">
-        <v>3.782186298066787</v>
+        <v>0.05742963058528803</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>1.530472201876815</v>
+        <v>0.3629738350326508</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>1.598442359002721</v>
+        <v>0.1687693563106734</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>1.565755411199661</v>
+        <v>0.1244808990153637</v>
       </c>
       <c r="AB58" s="156" t="n">
-        <v>2.449315332533725</v>
+        <v>0.1009172749009755</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>3.782186298066787</v>
+        <v>0.05742963058528803</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>4204.877524374548</v>
+        <v>997.2481166225549</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>4689.921633396324</v>
+        <v>495.1789789339862</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>4887.646869876646</v>
+        <v>388.5783642067765</v>
       </c>
       <c r="AG58" s="159" t="n">
-        <v>6774.155059191921</v>
+        <v>279.1103535138191</v>
       </c>
       <c r="AH58" s="160" t="n">
-        <v>11242.73376423273</v>
+        <v>170.7123858966582</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" thickTop="1">
@@ -6538,49 +6538,49 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>2.084745916604836</v>
+        <v>0.3022987255135206</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>2.313602031903233</v>
+        <v>0.1838592725706117</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>2.264041633815015</v>
+        <v>0.1346636740075247</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>3.183142625319547</v>
+        <v>0.09718013608057252</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>4.960114942316831</v>
+        <v>0.05548317283638751</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>2.084745916604836</v>
+        <v>0.3022987255135206</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>2.313602031903233</v>
+        <v>0.1838592725706117</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>2.264041633815015</v>
+        <v>0.1346636740075247</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>3.183142625319547</v>
+        <v>0.09718013608057252</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>4.960114942316831</v>
+        <v>0.05548317283638751</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>40664.66356419515</v>
+        <v>5896.582346549048</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>49324.37781582658</v>
+        <v>3919.751150009016</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>51653.60543891709</v>
+        <v>3072.321718933536</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>72534.51355501865</v>
+        <v>2214.451165884288</v>
       </c>
       <c r="Q59" s="166" t="n">
-        <v>120946.660959227</v>
+        <v>1352.892941398315</v>
       </c>
       <c r="S59" s="42" t="inlineStr">
         <is>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>2.582677407962217</v>
+        <v>0.3745013157819416</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>2.866457573633686</v>
+        <v>0.2277940618461789</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>2.805118149360287</v>
+        <v>0.1668465413250916</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>3.945604502810289</v>
+        <v>0.1204578077819343</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>6.148123823459464</v>
+        <v>0.06877207901097143</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>2.582677407962217</v>
+        <v>0.3745013157819416</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>2.866457573633686</v>
+        <v>0.2277940618461789</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>2.805118149360287</v>
+        <v>0.1668465413250916</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>3.945604502810289</v>
+        <v>0.1204578077819343</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>6.148123823459464</v>
+        <v>0.06877207901097143</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>40664.66356419515</v>
+        <v>5896.582346549048</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>49324.37781582658</v>
+        <v>3919.751150009016</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>51653.60543891709</v>
+        <v>3072.321718933536</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>72534.51355501865</v>
+        <v>2214.451165884288</v>
       </c>
       <c r="AH59" s="166" t="n">
-        <v>120946.660959227</v>
+        <v>1352.892941398315</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
@@ -6640,49 +6640,49 @@
         </is>
       </c>
       <c r="C60" s="155" t="n">
-        <v>0.9062285887663042</v>
+        <v>0.3507976023471663</v>
       </c>
       <c r="D60" s="156" t="n">
-        <v>0.6604342136030341</v>
+        <v>0</v>
       </c>
       <c r="E60" s="156" t="n">
-        <v>0.6381275922591123</v>
+        <v>0</v>
       </c>
       <c r="F60" s="156" t="n">
-        <v>0.8435823535159963</v>
+        <v>0</v>
       </c>
       <c r="G60" s="157" t="n">
-        <v>1.256060573174341</v>
+        <v>0</v>
       </c>
       <c r="H60" s="155" t="n">
-        <v>0.9062285887663042</v>
+        <v>0.3507976023471663</v>
       </c>
       <c r="I60" s="156" t="n">
-        <v>0.6604342136030341</v>
+        <v>0</v>
       </c>
       <c r="J60" s="156" t="n">
-        <v>0.6381275922591123</v>
+        <v>0</v>
       </c>
       <c r="K60" s="156" t="n">
-        <v>0.8435823535159963</v>
+        <v>0</v>
       </c>
       <c r="L60" s="157" t="n">
-        <v>1.256060573174341</v>
+        <v>0</v>
       </c>
       <c r="M60" s="158" t="n">
-        <v>85.44468261825483</v>
+        <v>33.07530811470345</v>
       </c>
       <c r="N60" s="159" t="n">
-        <v>68.04515979529718</v>
+        <v>0</v>
       </c>
       <c r="O60" s="159" t="n">
-        <v>72.79856307770595</v>
+        <v>0</v>
       </c>
       <c r="P60" s="159" t="n">
-        <v>105.3935595027948</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="160" t="n">
-        <v>178.7097751091651</v>
+        <v>0</v>
       </c>
       <c r="S60" s="32" t="inlineStr">
         <is>
@@ -6690,49 +6690,49 @@
         </is>
       </c>
       <c r="T60" s="155" t="n">
-        <v>0.927483417074256</v>
+        <v>0.3590252646623451</v>
       </c>
       <c r="U60" s="156" t="n">
-        <v>0.6759241418538515</v>
+        <v>0</v>
       </c>
       <c r="V60" s="156" t="n">
-        <v>0.6530943374933346</v>
+        <v>0</v>
       </c>
       <c r="W60" s="156" t="n">
-        <v>0.8633678671379067</v>
+        <v>0</v>
       </c>
       <c r="X60" s="157" t="n">
-        <v>1.285520416041969</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="155" t="n">
-        <v>0.927483417074256</v>
+        <v>0.3590252646623451</v>
       </c>
       <c r="Z60" s="156" t="n">
-        <v>0.6759241418538515</v>
+        <v>0</v>
       </c>
       <c r="AA60" s="156" t="n">
-        <v>0.6530943374933346</v>
+        <v>0</v>
       </c>
       <c r="AB60" s="156" t="n">
-        <v>0.8633678671379067</v>
+        <v>0</v>
       </c>
       <c r="AC60" s="157" t="n">
-        <v>1.285520416041969</v>
+        <v>0</v>
       </c>
       <c r="AD60" s="158" t="n">
-        <v>85.44468261825483</v>
+        <v>33.07530811470345</v>
       </c>
       <c r="AE60" s="159" t="n">
-        <v>68.04515979529718</v>
+        <v>0</v>
       </c>
       <c r="AF60" s="159" t="n">
-        <v>72.79856307770595</v>
+        <v>0</v>
       </c>
       <c r="AG60" s="159" t="n">
-        <v>105.3935595027948</v>
+        <v>0</v>
       </c>
       <c r="AH60" s="160" t="n">
-        <v>178.7097751091651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" thickTop="1">
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>2.079076674630635</v>
+        <v>0.3025320287172599</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>2.305651102906569</v>
+        <v>0.1829749993556333</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>2.255951970873241</v>
+        <v>0.133993660891592</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>3.170385359712996</v>
+        <v>0.0966502276090524</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>4.938627425878025</v>
+        <v>0.05516131050133897</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>2.079076674630635</v>
+        <v>0.3025320287172599</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>2.305651102906569</v>
+        <v>0.1829749993556333</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>2.255951970873241</v>
+        <v>0.133993660891592</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>3.170385359712996</v>
+        <v>0.0966502276090524</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>4.938627425878025</v>
+        <v>0.05516131050133897</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>40750.1082468134</v>
+        <v>5929.657654663752</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>49392.42297562188</v>
+        <v>3919.751150009016</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>51726.40400199479</v>
+        <v>3072.321718933536</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>72639.90711452145</v>
+        <v>2214.451165884288</v>
       </c>
       <c r="Q61" s="166" t="n">
-        <v>121125.3707343361</v>
+        <v>1352.892941398315</v>
       </c>
       <c r="S61" s="42" t="inlineStr">
         <is>
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>2.573049163551465</v>
+        <v>0.3744112917705489</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>2.85371668589714</v>
+        <v>0.2264691340788469</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>2.792169530214331</v>
+        <v>0.1658426340692679</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>3.925272567999575</v>
+        <v>0.1196632093831875</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>6.114002280843494</v>
+        <v>0.06828949607583382</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>2.573049163551465</v>
+        <v>0.3744112917705489</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>2.85371668589714</v>
+        <v>0.2264691340788469</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>2.792169530214331</v>
+        <v>0.1658426340692679</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>3.925272567999575</v>
+        <v>0.1196632093831875</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>6.114002280843494</v>
+        <v>0.06828949607583382</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>40750.1082468134</v>
+        <v>5929.657654663752</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>49392.42297562188</v>
+        <v>3919.751150009016</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>51726.40400199479</v>
+        <v>3072.321718933536</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>72639.90711452145</v>
+        <v>2214.451165884288</v>
       </c>
       <c r="AH61" s="166" t="n">
-        <v>121125.3707343361</v>
+        <v>1352.892941398315</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" thickBot="1">
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>2.078951109014448</v>
+        <v>0.3025137573273369</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>2.305520387800231</v>
+        <v>0.1829646258882566</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>2.255828845138147</v>
+        <v>0.1339863477624969</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>3.170208687168078</v>
+        <v>0.09664484168912746</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>4.938365113754571</v>
+        <v>0.055158380642647</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>2.078951109014448</v>
+        <v>0.3025137573273369</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>2.305520387800231</v>
+        <v>0.1829646258882566</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>2.255828845138147</v>
+        <v>0.1339863477624969</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>3.170208687168078</v>
+        <v>0.09664484168912746</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>4.938365113754571</v>
+        <v>0.055158380642647</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>40750.1082468134</v>
+        <v>5929.657654663752</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>49392.42297562188</v>
+        <v>3919.751150009016</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>51726.40400199479</v>
+        <v>3072.321718933536</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>72639.90711452145</v>
+        <v>2214.451165884288</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>121125.3707343361</v>
+        <v>1352.892941398315</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>2.572834192388689</v>
+        <v>0.3743800107395105</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>2.853492857471058</v>
+        <v>0.2264513711978687</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>2.79195870236073</v>
+        <v>0.1658301118186674</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>3.924969849002514</v>
+        <v>0.1196539808962221</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>6.113552902078222</v>
+        <v>0.06828447680236646</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>2.572834192388689</v>
+        <v>0.3743800107395105</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>2.853492857471058</v>
+        <v>0.2264513711978687</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>2.79195870236073</v>
+        <v>0.1658301118186674</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>3.924969849002514</v>
+        <v>0.1196539808962221</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>6.113552902078222</v>
+        <v>0.06828447680236646</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>40750.1082468134</v>
+        <v>5929.657654663752</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>49392.42297562188</v>
+        <v>3919.751150009016</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>51726.40400199479</v>
+        <v>3072.321718933536</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>72639.90711452145</v>
+        <v>2214.451165884288</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>121125.3707343361</v>
+        <v>1352.892941398315</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>2.570444806033084</v>
+        <v>2.461414484727278</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>3.132341759284621</v>
+        <v>3.030080509686511</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>3.626829298655868</v>
+        <v>3.529116794758978</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>1.897188373228605</v>
+        <v>1.796678743494891</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>1.866699602056987</v>
+        <v>1.789797449334842</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>2.570444806033084</v>
+        <v>2.461414484727278</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>3.132341759284621</v>
+        <v>3.030080509686511</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>3.626829298655868</v>
+        <v>3.529116794758978</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>1.897188373228605</v>
+        <v>1.796678743494891</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>1.866699602056987</v>
+        <v>1.789797449334842</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>41556.01925450973</v>
+        <v>39793.34140168245</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>55610.18380075933</v>
+        <v>53794.68366607895</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>68986.34602002121</v>
+        <v>67127.74500816446</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>36854.56767429125</v>
+        <v>34902.07892662129</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>38773.80016893084</v>
+        <v>37176.44154790616</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>3.197177635116332</v>
+        <v>3.061563244949192</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>3.896077828561178</v>
+        <v>3.768882963537527</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>4.511132661876712</v>
+        <v>4.389595630076959</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>2.359765991571796</v>
+        <v>2.23474983112197</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>2.321843365463161</v>
+        <v>2.226190721143212</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>3.197177635116332</v>
+        <v>3.061563244949192</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>3.896077828561178</v>
+        <v>3.768882963537527</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>4.511132661876712</v>
+        <v>4.389595630076959</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>2.359765991571796</v>
+        <v>2.23474983112197</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>2.321843365463161</v>
+        <v>2.226190721143212</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>41556.01925450973</v>
+        <v>39793.34140168245</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>55610.18380075933</v>
+        <v>53794.68366607895</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>68986.34602002121</v>
+        <v>67127.74500816446</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>36854.56767429125</v>
+        <v>34902.07892662129</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>38773.80016893084</v>
+        <v>37176.44154790616</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,49 +7399,49 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>10.12702461867599</v>
+        <v>9.986932697505695</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>13.20830829849626</v>
+        <v>13.07534751902397</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>16.00574358443767</v>
+        <v>15.88077432076285</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>3.923670317377309</v>
+        <v>3.767485886511329</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>4.193907719539093</v>
+        <v>4.075152977709541</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>10.12702461867599</v>
+        <v>9.986932697505695</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>13.20830829849626</v>
+        <v>13.07534751902397</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>16.00574358443767</v>
+        <v>15.88077432076285</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>3.923670317377309</v>
+        <v>3.767485886511329</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>4.193907719539093</v>
+        <v>4.075152977709541</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>33813.66523107428</v>
+        <v>33345.90480761341</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>47097.54627541833</v>
+        <v>46623.44116502165</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>60720.34532797831</v>
+        <v>60246.25446142861</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>13188.19680525928</v>
+        <v>12663.23144232971</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>15150.61833522349</v>
+        <v>14721.61324277113</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>12.3073441211407</v>
+        <v>12.13709080910126</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>16.05201938463983</v>
+        <v>15.89043252875693</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>19.4517345050326</v>
+        <v>19.2998597154942</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>4.768425340332717</v>
+        <v>4.578614847180837</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>5.096844084044925</v>
+        <v>4.952521785171656</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>12.3073441211407</v>
+        <v>12.13709080910126</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>16.05201938463983</v>
+        <v>15.89043252875693</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>19.4517345050326</v>
+        <v>19.2998597154942</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>4.768425340332717</v>
+        <v>4.578614847180837</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>5.096844084044925</v>
+        <v>4.952521785171656</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>33813.66523107428</v>
+        <v>33345.90480761341</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>47097.54627541833</v>
+        <v>46623.44116502165</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>60720.34532797831</v>
+        <v>60246.25446142861</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>13188.19680525928</v>
+        <v>12663.23144232971</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>15150.61833522349</v>
+        <v>14721.61324277113</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>3.863960210049903</v>
+        <v>3.749612845995352</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>4.817593723811096</v>
+        <v>4.710197835979606</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>5.685205261102898</v>
+        <v>5.582960480962241</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>2.196102915653492</v>
+        <v>2.087381020445072</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>2.211481589131021</v>
+        <v>2.128378865549637</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>3.863960210049903</v>
+        <v>3.749612845995352</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>4.817593723811096</v>
+        <v>4.710197835979606</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>5.685205261102898</v>
+        <v>5.582960480962241</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>2.196102915653492</v>
+        <v>2.087381020445072</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>2.211481589131021</v>
+        <v>2.128378865549637</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>75369.684485584</v>
+        <v>73139.24620929584</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>102707.7300761777</v>
+        <v>100418.1248311006</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>129706.6913479995</v>
+        <v>127373.9994695931</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>50042.76447955053</v>
+        <v>47565.310368951</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>53924.41850415433</v>
+        <v>51898.05479067729</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>4.78684844051066</v>
+        <v>4.645189760931772</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>5.968800090026033</v>
+        <v>5.835741010803818</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>7.043895404823349</v>
+        <v>6.917215451519388</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>2.722138016598415</v>
+        <v>2.587373838620261</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>2.74115878389859</v>
+        <v>2.638151930108539</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>4.78684844051066</v>
+        <v>4.645189760931772</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>5.968800090026033</v>
+        <v>5.835741010803818</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>7.043895404823349</v>
+        <v>6.917215451519388</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>2.722138016598415</v>
+        <v>2.587373838620261</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>2.74115878389859</v>
+        <v>2.638151930108539</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>75369.684485584</v>
+        <v>73139.24620929584</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>102707.7300761777</v>
+        <v>100418.1248311006</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>129706.6913479995</v>
+        <v>127373.9994695931</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>50042.76447955053</v>
+        <v>47565.310368951</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>53924.41850415433</v>
+        <v>51898.05479067729</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,46 +7603,46 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>7.214822337435814</v>
+        <v>7.214822337435819</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>8.783529712855097</v>
+        <v>8.783529712855096</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>10.17753349295959</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>8.713501568386059</v>
+        <v>8.713501568386064</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>9.320952109438556</v>
+        <v>9.32095210943856</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>7.214822337435814</v>
+        <v>7.214822337435819</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>8.783529712855097</v>
+        <v>8.783529712855096</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>10.17753349295959</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>8.713501568386059</v>
+        <v>8.713501568386064</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>9.320952109438556</v>
+        <v>9.32095210943856</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>680.2568495532994</v>
+        <v>680.2568495532998</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>904.9753488955529</v>
+        <v>904.9753488955527</v>
       </c>
       <c r="O71" s="159" t="n">
         <v>1161.068449241788</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>1088.627497004627</v>
+        <v>1088.627497004628</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>1326.166341700671</v>
@@ -7653,46 +7653,46 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>7.384039918910855</v>
+        <v>7.38403991891086</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>8.98954000462782</v>
+        <v>8.989540004627816</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>10.4162389693403</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>8.917869409009185</v>
+        <v>8.917869409009191</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>9.539567190896605</v>
+        <v>9.539567190896607</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>7.384039918910855</v>
+        <v>7.38403991891086</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>8.98954000462782</v>
+        <v>8.989540004627816</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>10.4162389693403</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>8.917869409009185</v>
+        <v>8.917869409009191</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>9.539567190896605</v>
+        <v>9.539567190896607</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>680.2568495532994</v>
+        <v>680.2568495532998</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>904.9753488955529</v>
+        <v>904.9753488955527</v>
       </c>
       <c r="AF71" s="159" t="n">
         <v>1161.068449241788</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>1088.627497004627</v>
+        <v>1088.627497004628</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>1326.166341700671</v>
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>3.880079487869247</v>
+        <v>3.766282190292824</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>4.836667937030795</v>
+        <v>4.729788570915508</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>5.707556640259916</v>
+        <v>5.605820574471772</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>2.231641297236878</v>
+        <v>2.123512245953505</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>2.252724197757114</v>
+        <v>2.170103559739575</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>3.880079487869247</v>
+        <v>3.766282190292824</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>4.836667937030795</v>
+        <v>4.729788570915508</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>5.707556640259916</v>
+        <v>5.605820574471772</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>2.231641297236878</v>
+        <v>2.123512245953505</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>2.252724197757114</v>
+        <v>2.170103559739575</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>76049.94133513731</v>
+        <v>73819.50305884915</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>103612.7054250732</v>
+        <v>101323.1001799962</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>130867.7597972413</v>
+        <v>128535.0679188349</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>51131.39197655515</v>
+        <v>48653.93786595562</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>55250.584845855</v>
+        <v>53224.22113237796</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>4.801956273473579</v>
+        <v>4.661121620804767</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>5.986369741132418</v>
+        <v>5.854084578786387</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>7.064186626605121</v>
+        <v>6.93826890021506</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.763008080018354</v>
+        <v>2.629132872228199</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>2.788864130755851</v>
+        <v>2.686580089923561</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>4.801956273473579</v>
+        <v>4.661121620804767</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>5.986369741132418</v>
+        <v>5.854084578786387</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>7.064186626605121</v>
+        <v>6.93826890021506</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>2.763008080018354</v>
+        <v>2.629132872228199</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>2.788864130755851</v>
+        <v>2.686580089923561</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>76049.94133513731</v>
+        <v>73819.50305884915</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>103612.7054250732</v>
+        <v>101323.1001799962</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>130867.7597972413</v>
+        <v>128535.0679188349</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>51131.39197655515</v>
+        <v>48653.93786595562</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>55250.584845855</v>
+        <v>53224.22113237796</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>3.882982593231814</v>
+        <v>3.769192168431161</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>4.839458512874285</v>
+        <v>4.732585206109301</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>5.710325007951186</v>
+        <v>5.608594494731558</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>2.234801085641196</v>
+        <v>2.12667805994541</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>2.255873181032566</v>
+        <v>2.173256931358818</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>3.882982593231814</v>
+        <v>3.769192168431161</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>4.839458512874285</v>
+        <v>4.732585206109301</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>5.710325007951186</v>
+        <v>5.608594494731558</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>2.234801085641196</v>
+        <v>2.12667805994541</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>2.255873181032566</v>
+        <v>2.173256931358818</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>76111.43922942008</v>
+        <v>73881.00095313194</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>103678.3639414827</v>
+        <v>101388.7586964057</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>130938.3816864388</v>
+        <v>128605.6898080324</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>51206.64262182103</v>
+        <v>48729.18851122149</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>55330.75604741432</v>
+        <v>53304.39233393729</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>4.805437867681707</v>
+        <v>4.664614981359795</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>5.989693421748582</v>
+        <v>5.857418635057508</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>7.067465084338467</v>
+        <v>6.941556865596025</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>2.766861031945286</v>
+        <v>2.632996148678571</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>2.792705625230019</v>
+        <v>2.690429102267999</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>4.805437867681707</v>
+        <v>4.664614981359795</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>5.989693421748582</v>
+        <v>5.857418635057508</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>7.067465084338467</v>
+        <v>6.941556865596025</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>2.766861031945286</v>
+        <v>2.632996148678571</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>2.792705625230019</v>
+        <v>2.690429102267999</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>76111.43922942008</v>
+        <v>73881.00095313194</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>103678.3639414827</v>
+        <v>101388.7586964057</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>130938.3816864388</v>
+        <v>128605.6898080324</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>51206.64262182103</v>
+        <v>48729.18851122149</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>55330.75604741432</v>
+        <v>53304.39233393729</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>447.4846268980029</v>
+        <v>445.4153840909526</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>492.3879484324645</v>
+        <v>489.9563218111653</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>534.0489118787137</v>
+        <v>531.6252142078656</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>610.7582063062259</v>
+        <v>607.3630064959405</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>661.3108862382591</v>
+        <v>655.9999634670118</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>447.4846268980029</v>
+        <v>445.4153840909526</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>492.3879484324644</v>
+        <v>489.9563218111653</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>534.0489118787139</v>
+        <v>531.6252142078656</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>610.7582063062259</v>
+        <v>607.3630064959403</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>661.3108862382591</v>
+        <v>655.9999634670118</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>7234420.956180287</v>
+        <v>7200967.79907292</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>8741633.709810048</v>
+        <v>8698463.706746222</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>10158207.07087999</v>
+        <v>10112105.63284677</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>11864520.13124859</v>
+        <v>11798565.3621062</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>13736294.8619507</v>
+        <v>13625980.02713848</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>556.5915431518731</v>
+        <v>554.0177719474501</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>612.4433144155313</v>
+        <v>609.4188019917189</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>664.262167041785</v>
+        <v>661.2475168266425</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>759.6749298342645</v>
+        <v>755.451903191281</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>822.5535013929842</v>
+        <v>815.9476550172099</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>556.5915431518731</v>
+        <v>554.0177719474501</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>612.4433144155313</v>
+        <v>609.4188019917189</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>664.262167041785</v>
+        <v>661.2475168266425</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>759.6749298342645</v>
+        <v>755.451903191281</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>822.5535013929842</v>
+        <v>815.9476550172099</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>7234420.956180287</v>
+        <v>7200967.79907292</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>8741633.709810048</v>
+        <v>8698463.706746222</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>10158207.07087999</v>
+        <v>10112105.63284677</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>11864520.13124859</v>
+        <v>11798565.3621062</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>13736294.8619507</v>
+        <v>13625980.02713848</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>876.9435092566652</v>
+        <v>875.8427482758733</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>985.9348984950292</v>
+        <v>984.6255398223632</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1075.018356987064</v>
+        <v>1073.707443597387</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1373.806323966459</v>
+        <v>1371.717774216966</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1482.146133808398</v>
+        <v>1478.962485284541</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>876.9435092566652</v>
+        <v>875.8427482758733</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>985.9348984950291</v>
+        <v>984.6255398223632</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>1075.018356987064</v>
+        <v>1073.707443597387</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>1373.806323966459</v>
+        <v>1371.717774216966</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1482.146133808399</v>
+        <v>1478.962485284541</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>2928073.6805837</v>
+        <v>2924398.290752487</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>3515598.928873129</v>
+        <v>3510930.08110827</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>4078253.879665893</v>
+        <v>4073280.720293673</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>4617622.457355195</v>
+        <v>4610602.447286586</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>5354297.684171736</v>
+        <v>5342796.657700947</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>1065.746944400493</v>
+        <v>1064.40919272161</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1198.203868729874</v>
+        <v>1196.612608871299</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1306.466741631447</v>
+        <v>1304.873592329725</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1669.582905296131</v>
+        <v>1667.044696745347</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1801.247967044349</v>
+        <v>1797.378888077995</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>1065.746944400493</v>
+        <v>1064.40919272161</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>1198.203868729874</v>
+        <v>1196.612608871299</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1306.466741631447</v>
+        <v>1304.873592329725</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1669.582905296131</v>
+        <v>1667.044696745347</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1801.247967044349</v>
+        <v>1797.378888077995</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>2928073.6805837</v>
+        <v>2924398.290752487</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>3515598.928873129</v>
+        <v>3510930.08110827</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>4078253.879665893</v>
+        <v>4073280.720293673</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>4617622.457355195</v>
+        <v>4610602.447286586</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>5354297.684171736</v>
+        <v>5342796.657700947</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>520.9982658055613</v>
+        <v>519.0948051634369</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>574.9359565011837</v>
+        <v>572.6920343802715</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>624.0017523720278</v>
+        <v>621.7630893789285</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>723.3109875422787</v>
+        <v>720.1085240680652</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>782.9197812879369</v>
+        <v>777.9240197764655</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>520.9982658055613</v>
+        <v>519.0948051634369</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>574.9359565011837</v>
+        <v>572.6920343802715</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>624.0017523720278</v>
+        <v>621.7630893789285</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>723.3109875422787</v>
+        <v>720.1085240680652</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>782.9197812879369</v>
+        <v>777.9240197764655</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>10162494.63676399</v>
+        <v>10125366.08982541</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>12257232.63868318</v>
+        <v>12209393.78785449</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>14236460.95054589</v>
+        <v>14185386.35314045</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>16482142.58860378</v>
+        <v>16409167.80939279</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>19090592.54612244</v>
+        <v>18968776.68483942</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>645.4361847965046</v>
+        <v>643.078091775094</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>712.3219569060592</v>
+        <v>709.5418298706237</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>773.1300585059896</v>
+        <v>770.3563841625269</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>896.5665147010109</v>
+        <v>892.5969614037646</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>970.4387529668205</v>
+        <v>964.2464447799759</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>645.4361847965046</v>
+        <v>643.078091775094</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>712.3219569060592</v>
+        <v>709.5418298706237</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>773.1300585059896</v>
+        <v>770.3563841625269</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>896.5665147010109</v>
+        <v>892.5969614037646</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>970.4387529668205</v>
+        <v>964.2464447799759</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>10162494.63676399</v>
+        <v>10125366.08982541</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>12257232.63868318</v>
+        <v>12209393.78785449</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>14236460.95054589</v>
+        <v>14185386.35314045</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>16482142.58860378</v>
+        <v>16409167.80939279</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>19090592.54612244</v>
+        <v>18968776.68483942</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>1181.578410078496</v>
+        <v>1181.022979092077</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>1326.83646075359</v>
+        <v>1326.176026539986</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1434.958633409061</v>
+        <v>1434.320505816802</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1575.8435404586</v>
+        <v>1574.999958105084</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1678.125983014899</v>
+        <v>1676.869922441725</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>1181.578410078496</v>
+        <v>1181.022979092077</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>1326.836460753589</v>
+        <v>1326.176026539986</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>1434.958633409061</v>
+        <v>1434.320505816802</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>1575.843540458599</v>
+        <v>1574.999958105084</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1678.125983014899</v>
+        <v>1676.869922441725</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>111406.3200932347</v>
+        <v>111353.9507187312</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>136705.2117146551</v>
+        <v>136637.1665548598</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>163702.2561872094</v>
+        <v>163629.4576241317</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>196879.1301242753</v>
+        <v>196773.7365647725</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>238760.3937535691</v>
+        <v>238581.6839784599</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1209.291336540892</v>
+        <v>1208.72287838848</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1357.956292455699</v>
+        <v>1357.280368313845</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1468.614379608421</v>
+        <v>1467.961285270928</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1612.803623497074</v>
+        <v>1611.940255629936</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1717.485014599471</v>
+        <v>1716.199494183428</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>1209.291336540892</v>
+        <v>1208.72287838848</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>1357.956292455699</v>
+        <v>1357.280368313845</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>1468.614379608421</v>
+        <v>1467.961285270928</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>1612.803623497074</v>
+        <v>1611.940255629936</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1717.485014599471</v>
+        <v>1716.199494183428</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>111406.3200932347</v>
+        <v>111353.9507187312</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>136705.2117146551</v>
+        <v>136637.1665548598</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>163702.2561872094</v>
+        <v>163629.4576241317</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>196879.1301242753</v>
+        <v>196773.7365647725</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>238760.3937535691</v>
+        <v>238581.6839784599</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>524.1759778279251</v>
+        <v>522.2790018645798</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>578.5522303335727</v>
+        <v>576.3159240153507</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>628.0366322366631</v>
+        <v>625.8059326362082</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>727.9597176249622</v>
+        <v>724.7701167699996</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>788.1129442544355</v>
+        <v>783.1388770480094</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>524.1759778279251</v>
+        <v>522.2790018645798</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>578.5522303335727</v>
+        <v>576.3159240153507</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>628.0366322366631</v>
+        <v>625.8059326362082</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>727.9597176249622</v>
+        <v>724.7701167699996</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>788.1129442544355</v>
+        <v>783.1388770480094</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>10273900.95685722</v>
+        <v>10236720.04054414</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>12393937.85039783</v>
+        <v>12346030.95440935</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>14400163.2067331</v>
+        <v>14349015.81076458</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>16679021.71872805</v>
+        <v>16605941.54595756</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>19329352.93987601</v>
+        <v>19207358.36881788</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>648.7161237300336</v>
+        <v>646.3684409940759</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>716.0771858693597</v>
+        <v>713.3092975938778</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>777.3147527209327</v>
+        <v>774.5538378008157</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>901.2911636901624</v>
+        <v>897.342100305645</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>975.680877137078</v>
+        <v>969.5230005404745</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>648.7161237300336</v>
+        <v>646.3684409940759</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>716.0771858693597</v>
+        <v>713.3092975938778</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>777.3147527209327</v>
+        <v>774.5538378008157</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>901.2911636901624</v>
+        <v>897.342100305645</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>975.680877137078</v>
+        <v>969.5230005404745</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>10273900.95685722</v>
+        <v>10236720.04054414</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>12393937.85039783</v>
+        <v>12346030.95440935</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>14400163.2067331</v>
+        <v>14349015.81076458</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>16679021.71872805</v>
+        <v>16605941.54595756</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>19329352.93987601</v>
+        <v>19207358.36881788</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>524.1692543536039</v>
+        <v>522.2723929579216</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>578.5449827469699</v>
+        <v>576.3088032124656</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>628.0288233180944</v>
+        <v>625.7982454651465</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>727.9481538322015</v>
+        <v>724.7587307205845</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>788.1007497452332</v>
+        <v>783.1269467332922</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>524.1692543536039</v>
+        <v>522.2723929579216</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>578.5449827469699</v>
+        <v>576.3088032124656</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>628.0288233180944</v>
+        <v>625.7982454651465</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>727.9481538322015</v>
+        <v>724.7587307205845</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>788.1007497452332</v>
+        <v>783.1269467332922</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>10274389.69677684</v>
+        <v>10237208.78046376</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>12394485.2751995</v>
+        <v>12346578.37921102</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>14400770.12485393</v>
+        <v>14349622.72888541</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>16679686.25932764</v>
+        <v>16606606.08655714</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>19330080.56107935</v>
+        <v>19208085.99002122</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>648.6927827942794</v>
+        <v>646.3452962007409</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>716.0526468253641</v>
+        <v>713.2849756464425</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>777.2888188638012</v>
+        <v>774.5281124116016</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>901.2575629463455</v>
+        <v>897.3088041155851</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>975.6458898341483</v>
+        <v>969.4884658410692</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>648.6927827942794</v>
+        <v>646.3452962007409</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>716.0526468253641</v>
+        <v>713.2849756464425</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>777.2888188638012</v>
+        <v>774.5281124116016</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>901.2575629463455</v>
+        <v>897.3088041155851</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>975.6458898341483</v>
+        <v>969.4884658410692</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>10274389.69677684</v>
+        <v>10237208.78046376</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>12394485.2751995</v>
+        <v>12346578.37921102</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>14400770.12485393</v>
+        <v>14349622.72888541</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>16679686.25932764</v>
+        <v>16606606.08655714</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>19330080.56107935</v>
+        <v>19208085.99002122</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
